--- a/data/payment-10-2026.xlsx
+++ b/data/payment-10-2026.xlsx
@@ -362,14 +362,14 @@
       </c>
       <c t="inlineStr" r="Q3">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">ยิ่งใช้ยิ่งได้</t>
+          <t xml:space="preserve">จำนวนยอดขาย</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
@@ -378,19 +378,19 @@
         </is>
       </c>
       <c r="D4" s="65">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E4" s="65">
         <v>0</v>
       </c>
       <c r="F4" s="65">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G4" s="65">
         <v>0</v>
       </c>
       <c r="H4" s="66">
-        <v>150.00</v>
+        <v>0.00</v>
       </c>
       <c r="I4" s="65">
         <v>0</v>
@@ -405,7 +405,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="65">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="O4" s="65">
         <v>0</v>
@@ -422,7 +422,7 @@
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">โอนเงิน</t>
+          <t xml:space="preserve">ยิ่งใช้ยิ่งได้</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
@@ -430,20 +430,20 @@
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D5" s="63">
-        <v>25600</v>
+      <c r="D5" s="65">
+        <v>150</v>
       </c>
       <c r="E5" s="65">
         <v>0</v>
       </c>
-      <c r="F5" s="63">
-        <v>25600</v>
+      <c r="F5" s="65">
+        <v>150</v>
       </c>
       <c r="G5" s="65">
         <v>0</v>
       </c>
       <c r="H5" s="66">
-        <v>25600.00</v>
+        <v>150.00</v>
       </c>
       <c r="I5" s="65">
         <v>0</v>
@@ -457,8 +457,8 @@
       <c r="L5" s="65">
         <v>0</v>
       </c>
-      <c r="N5" s="63">
-        <v>25600</v>
+      <c r="N5" s="65">
+        <v>150</v>
       </c>
       <c r="O5" s="65">
         <v>0</v>
@@ -475,7 +475,7 @@
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">ไทยช่วยไทย พลัส (หน้าร้าน)</t>
+          <t xml:space="preserve">โอนเงิน</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="D6" s="63">
-        <v>380874</v>
-      </c>
-      <c r="E6" s="63">
-        <v>1210</v>
+        <v>25600</v>
+      </c>
+      <c r="E6" s="65">
+        <v>0</v>
       </c>
       <c r="F6" s="63">
-        <v>379664</v>
+        <v>25600</v>
       </c>
       <c r="G6" s="65">
         <v>0</v>
       </c>
       <c r="H6" s="66">
-        <v>379664.00</v>
+        <v>25600.00</v>
       </c>
       <c r="I6" s="65">
         <v>0</v>
@@ -510,17 +510,14 @@
       <c r="L6" s="65">
         <v>0</v>
       </c>
-      <c r="M6" s="65">
-        <v>0</v>
-      </c>
       <c r="N6" s="63">
-        <v>379664</v>
+        <v>25600</v>
       </c>
       <c r="O6" s="65">
         <v>0</v>
       </c>
       <c r="P6" s="65">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q6">
         <is>
@@ -531,7 +528,7 @@
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">Cash</t>
+          <t xml:space="preserve">ไทยช่วยไทย พลัส (หน้าร้าน)</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
@@ -540,19 +537,19 @@
         </is>
       </c>
       <c r="D7" s="63">
-        <v>234038</v>
+        <v>394590</v>
       </c>
       <c r="E7" s="63">
-        <v>2225</v>
+        <v>1340</v>
       </c>
       <c r="F7" s="63">
-        <v>231813</v>
+        <v>393250</v>
       </c>
       <c r="G7" s="65">
         <v>0</v>
       </c>
       <c r="H7" s="66">
-        <v>231813.00</v>
+        <v>393250.00</v>
       </c>
       <c r="I7" s="65">
         <v>0</v>
@@ -570,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="63">
-        <v>231813</v>
+        <v>393250</v>
       </c>
       <c r="O7" s="65">
         <v>0</v>
       </c>
       <c r="P7" s="65">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c t="inlineStr" r="Q7">
         <is>
@@ -595,20 +592,20 @@
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D8" s="65">
-        <v>0</v>
+      <c r="D8" s="63">
+        <v>79058</v>
       </c>
       <c r="E8" s="65">
         <v>0</v>
       </c>
-      <c r="F8" s="65">
-        <v>0</v>
+      <c r="F8" s="63">
+        <v>79058</v>
       </c>
       <c r="G8" s="65">
         <v>0</v>
       </c>
       <c r="H8" s="66">
-        <v>0.00</v>
+        <v>79058.00</v>
       </c>
       <c r="I8" s="65">
         <v>0</v>
@@ -617,23 +614,26 @@
         <v>0</v>
       </c>
       <c r="K8" s="65">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="65">
-        <v>0</v>
-      </c>
-      <c r="N8" s="65">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="M8" s="65">
+        <v>0</v>
+      </c>
+      <c r="N8" s="63">
+        <v>78964</v>
       </c>
       <c r="O8" s="65">
         <v>0</v>
       </c>
       <c r="P8" s="65">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c t="inlineStr" r="Q8">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="D9" s="63">
-        <v>66435</v>
-      </c>
-      <c r="E9" s="65">
-        <v>0</v>
+        <v>258658</v>
+      </c>
+      <c r="E9" s="63">
+        <v>2435</v>
       </c>
       <c r="F9" s="63">
-        <v>66435</v>
+        <v>256223</v>
       </c>
       <c r="G9" s="65">
         <v>0</v>
       </c>
       <c r="H9" s="66">
-        <v>66435.00</v>
+        <v>256223.00</v>
       </c>
       <c r="I9" s="65">
         <v>0</v>
@@ -670,33 +670,33 @@
         <v>0</v>
       </c>
       <c r="K9" s="65">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="65">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M9" s="65">
         <v>0</v>
       </c>
       <c r="N9" s="63">
-        <v>66341</v>
+        <v>256223</v>
       </c>
       <c r="O9" s="65">
         <v>0</v>
       </c>
       <c r="P9" s="65">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c t="inlineStr" r="Q9">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">GRAB</t>
+          <t xml:space="preserve">Cash</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="D10" s="65">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E10" s="65">
         <v>0</v>
       </c>
       <c r="F10" s="65">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="G10" s="65">
         <v>0</v>
       </c>
       <c r="H10" s="66">
-        <v>135.00</v>
+        <v>0.00</v>
       </c>
       <c r="I10" s="65">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="65">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="O10" s="65">
         <v>0</v>
@@ -742,7 +742,7 @@
       </c>
       <c t="inlineStr" r="Q10">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
@@ -757,20 +757,20 @@
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D11" s="63">
-        <v>273934</v>
+      <c r="D11" s="65">
+        <v>135</v>
       </c>
       <c r="E11" s="65">
-        <v>93</v>
-      </c>
-      <c r="F11" s="63">
-        <v>273841</v>
+        <v>0</v>
+      </c>
+      <c r="F11" s="65">
+        <v>135</v>
       </c>
       <c r="G11" s="65">
         <v>0</v>
       </c>
       <c r="H11" s="66">
-        <v>273841.00</v>
+        <v>135.00</v>
       </c>
       <c r="I11" s="65">
         <v>0</v>
@@ -784,21 +784,18 @@
       <c r="L11" s="65">
         <v>0</v>
       </c>
-      <c r="M11" s="65">
-        <v>0</v>
-      </c>
-      <c r="N11" s="63">
-        <v>273841</v>
+      <c r="N11" s="65">
+        <v>135</v>
       </c>
       <c r="O11" s="65">
         <v>0</v>
       </c>
-      <c r="P11" s="63">
-        <v>2372</v>
+      <c r="P11" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q11">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -814,19 +811,19 @@
         </is>
       </c>
       <c r="D12" s="63">
-        <v>212191</v>
-      </c>
-      <c r="E12" s="63">
-        <v>13072</v>
+        <v>318481</v>
+      </c>
+      <c r="E12" s="65">
+        <v>93</v>
       </c>
       <c r="F12" s="63">
-        <v>199119</v>
+        <v>318388</v>
       </c>
       <c r="G12" s="65">
         <v>0</v>
       </c>
       <c r="H12" s="66">
-        <v>199119.00</v>
+        <v>318388.00</v>
       </c>
       <c r="I12" s="65">
         <v>0</v>
@@ -844,45 +841,45 @@
         <v>0</v>
       </c>
       <c r="N12" s="63">
-        <v>199119</v>
+        <v>318388</v>
       </c>
       <c r="O12" s="65">
         <v>0</v>
       </c>
-      <c r="P12" s="65">
-        <v>736</v>
+      <c r="P12" s="63">
+        <v>2841</v>
       </c>
       <c t="inlineStr" r="Q12">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">K Plus</t>
+          <t xml:space="preserve">GRAB</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Dynamic QR</t>
+          <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
       <c r="D13" s="63">
-        <v>219307</v>
+        <v>260639</v>
       </c>
       <c r="E13" s="63">
-        <v>1000</v>
+        <v>16530</v>
       </c>
       <c r="F13" s="63">
-        <v>218307</v>
+        <v>244109</v>
       </c>
       <c r="G13" s="65">
         <v>0</v>
       </c>
       <c r="H13" s="66">
-        <v>218307.00</v>
+        <v>244109.00</v>
       </c>
       <c r="I13" s="65">
         <v>0</v>
@@ -896,18 +893,21 @@
       <c r="L13" s="65">
         <v>0</v>
       </c>
+      <c r="M13" s="65">
+        <v>0</v>
+      </c>
       <c r="N13" s="63">
-        <v>218307</v>
+        <v>244109</v>
       </c>
       <c r="O13" s="65">
         <v>0</v>
       </c>
       <c r="P13" s="65">
-        <v>0</v>
+        <v>887</v>
       </c>
       <c t="inlineStr" r="Q13">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="D14" s="63">
-        <v>435276</v>
-      </c>
-      <c r="E14" s="65">
-        <v>0</v>
+        <v>247657</v>
+      </c>
+      <c r="E14" s="63">
+        <v>1230</v>
       </c>
       <c r="F14" s="63">
-        <v>435276</v>
+        <v>246427</v>
       </c>
       <c r="G14" s="65">
         <v>0</v>
       </c>
       <c r="H14" s="66">
-        <v>435276.00</v>
+        <v>246427.00</v>
       </c>
       <c r="I14" s="65">
         <v>0</v>
@@ -944,13 +944,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="65">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="L14" s="65">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N14" s="63">
-        <v>434476</v>
+        <v>246427</v>
       </c>
       <c r="O14" s="65">
         <v>0</v>
@@ -960,35 +960,35 @@
       </c>
       <c t="inlineStr" r="Q14">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">LINEMAN</t>
+          <t xml:space="preserve">K Plus</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">บันทึกเอง</t>
+          <t xml:space="preserve">Dynamic QR</t>
         </is>
       </c>
       <c r="D15" s="63">
-        <v>108857</v>
-      </c>
-      <c r="E15" s="64">
-        <v>3239.50</v>
-      </c>
-      <c r="F15" s="64">
-        <v>105617.50</v>
+        <v>512003</v>
+      </c>
+      <c r="E15" s="65">
+        <v>0</v>
+      </c>
+      <c r="F15" s="63">
+        <v>512003</v>
       </c>
       <c r="G15" s="65">
         <v>0</v>
       </c>
       <c r="H15" s="66">
-        <v>105617.50</v>
+        <v>512003.00</v>
       </c>
       <c r="I15" s="65">
         <v>0</v>
@@ -997,49 +997,51 @@
         <v>0</v>
       </c>
       <c r="K15" s="65">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L15" s="65">
-        <v>0</v>
-      </c>
-      <c r="M15" s="65">
-        <v>0</v>
-      </c>
-      <c r="N15" s="64">
-        <v>105617.50</v>
+        <v>800</v>
+      </c>
+      <c r="N15" s="63">
+        <v>511203</v>
       </c>
       <c r="O15" s="65">
         <v>0</v>
       </c>
-      <c r="P15" s="64">
-        <v>1347.50</v>
+      <c r="P15" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q15">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">Line Man - Rabbit Linepay</t>
+          <t xml:space="preserve">LINEMAN</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
       <c r="D16" s="63">
-        <v>278277</v>
-      </c>
-      <c r="E16" s="63">
-        <v>22730</v>
-      </c>
-      <c r="F16" s="63">
-        <v>255547</v>
+        <v>130453</v>
+      </c>
+      <c r="E16" s="64">
+        <v>3989.50</v>
+      </c>
+      <c r="F16" s="64">
+        <v>126463.50</v>
       </c>
       <c r="G16" s="65">
         <v>0</v>
       </c>
       <c r="H16" s="66">
-        <v>255547.00</v>
+        <v>126463.50</v>
       </c>
       <c r="I16" s="65">
         <v>0</v>
@@ -1053,49 +1055,44 @@
       <c r="L16" s="65">
         <v>0</v>
       </c>
-      <c r="M16" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="N16" s="63">
-        <v>255547</v>
+      <c r="M16" s="65">
+        <v>0</v>
+      </c>
+      <c r="N16" s="64">
+        <v>126463.50</v>
       </c>
       <c r="O16" s="65">
         <v>0</v>
       </c>
-      <c r="P16" s="65">
-        <v>0</v>
+      <c r="P16" s="64">
+        <v>1542.50</v>
       </c>
       <c t="inlineStr" r="Q16">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">PromptPay</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B17">
-        <is>
-          <t xml:space="preserve">บันทึกเอง</t>
+          <t xml:space="preserve">Line Man - Rabbit Linepay</t>
         </is>
       </c>
       <c r="D17" s="63">
-        <v>1507</v>
-      </c>
-      <c r="E17" s="65">
-        <v>0</v>
+        <v>342840</v>
+      </c>
+      <c r="E17" s="63">
+        <v>27820</v>
       </c>
       <c r="F17" s="63">
-        <v>1507</v>
+        <v>315020</v>
       </c>
       <c r="G17" s="65">
         <v>0</v>
       </c>
       <c r="H17" s="66">
-        <v>1507.00</v>
+        <v>315020.00</v>
       </c>
       <c r="I17" s="65">
         <v>0</v>
@@ -1109,8 +1106,11 @@
       <c r="L17" s="65">
         <v>0</v>
       </c>
+      <c r="M17" s="66">
+        <v>0.00</v>
+      </c>
       <c r="N17" s="63">
-        <v>1507</v>
+        <v>315020</v>
       </c>
       <c r="O17" s="65">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">SHOPEE</t>
+          <t xml:space="preserve">PromptPay</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
@@ -1136,19 +1136,19 @@
         </is>
       </c>
       <c r="D18" s="63">
-        <v>32796</v>
+        <v>1507</v>
       </c>
       <c r="E18" s="65">
         <v>0</v>
       </c>
       <c r="F18" s="63">
-        <v>32796</v>
+        <v>1507</v>
       </c>
       <c r="G18" s="65">
         <v>0</v>
       </c>
       <c r="H18" s="66">
-        <v>32796.00</v>
+        <v>1507.00</v>
       </c>
       <c r="I18" s="65">
         <v>0</v>
@@ -1162,28 +1162,25 @@
       <c r="L18" s="65">
         <v>0</v>
       </c>
-      <c r="M18" s="65">
-        <v>0</v>
-      </c>
       <c r="N18" s="63">
-        <v>32796</v>
+        <v>1507</v>
       </c>
       <c r="O18" s="65">
         <v>0</v>
       </c>
       <c r="P18" s="65">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q18">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">Split Amount</t>
+          <t xml:space="preserve">SHOPEE</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
@@ -1192,19 +1189,19 @@
         </is>
       </c>
       <c r="D19" s="63">
-        <v>2226</v>
+        <v>39291</v>
       </c>
       <c r="E19" s="65">
         <v>0</v>
       </c>
       <c r="F19" s="63">
-        <v>2226</v>
+        <v>39291</v>
       </c>
       <c r="G19" s="65">
         <v>0</v>
       </c>
       <c r="H19" s="66">
-        <v>2226.00</v>
+        <v>39291.00</v>
       </c>
       <c r="I19" s="65">
         <v>0</v>
@@ -1218,122 +1215,178 @@
       <c r="L19" s="65">
         <v>0</v>
       </c>
+      <c r="M19" s="65">
+        <v>0</v>
+      </c>
       <c r="N19" s="63">
-        <v>2226</v>
+        <v>39291</v>
       </c>
       <c r="O19" s="65">
         <v>0</v>
       </c>
       <c r="P19" s="65">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c t="inlineStr" r="Q19">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
+          <t xml:space="preserve">Split Amount</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">บันทึกเอง</t>
+        </is>
+      </c>
+      <c r="D20" s="63">
+        <v>2844</v>
+      </c>
+      <c r="E20" s="65">
+        <v>0</v>
+      </c>
+      <c r="F20" s="63">
+        <v>2844</v>
+      </c>
+      <c r="G20" s="65">
+        <v>0</v>
+      </c>
+      <c r="H20" s="66">
+        <v>2844.00</v>
+      </c>
+      <c r="I20" s="65">
+        <v>0</v>
+      </c>
+      <c r="J20" s="65">
+        <v>0</v>
+      </c>
+      <c r="K20" s="65">
+        <v>0</v>
+      </c>
+      <c r="L20" s="65">
+        <v>0</v>
+      </c>
+      <c r="N20" s="63">
+        <v>2844</v>
+      </c>
+      <c r="O20" s="65">
+        <v>0</v>
+      </c>
+      <c r="P20" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="Q20">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c t="inlineStr" r="A21">
+        <is>
           <t xml:space="preserve">VISA</t>
         </is>
       </c>
-      <c t="inlineStr" r="B20">
-        <is>
-          <t xml:space="preserve">บันทึกเอง</t>
-        </is>
-      </c>
-      <c r="D20" s="65">
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">บันทึกเอง</t>
+        </is>
+      </c>
+      <c r="D21" s="65">
         <v>48</v>
       </c>
-      <c r="E20" s="65">
-        <v>0</v>
-      </c>
-      <c r="F20" s="65">
+      <c r="E21" s="65">
+        <v>0</v>
+      </c>
+      <c r="F21" s="65">
         <v>48</v>
       </c>
-      <c r="G20" s="65">
-        <v>0</v>
-      </c>
-      <c r="H20" s="66">
+      <c r="G21" s="65">
+        <v>0</v>
+      </c>
+      <c r="H21" s="66">
         <v>48.00</v>
       </c>
-      <c r="I20" s="65">
-        <v>0</v>
-      </c>
-      <c r="J20" s="65">
-        <v>0</v>
-      </c>
-      <c r="K20" s="65">
-        <v>0</v>
-      </c>
-      <c r="L20" s="65">
-        <v>0</v>
-      </c>
-      <c r="N20" s="65">
+      <c r="I21" s="65">
+        <v>0</v>
+      </c>
+      <c r="J21" s="65">
+        <v>0</v>
+      </c>
+      <c r="K21" s="65">
+        <v>0</v>
+      </c>
+      <c r="L21" s="65">
+        <v>0</v>
+      </c>
+      <c r="N21" s="65">
         <v>48</v>
       </c>
-      <c r="O20" s="65">
-        <v>0</v>
-      </c>
-      <c r="P20" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="Q20">
+      <c r="O21" s="65">
+        <v>0</v>
+      </c>
+      <c r="P21" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="Q21">
         <is>
           <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c t="inlineStr" r="A21" s="2">
+    <row r="22">
+      <c t="inlineStr" r="A22" s="2">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="D21" s="2">
-        <v>2271651.00</v>
-      </c>
-      <c r="E21" s="2">
-        <v>43569.50</v>
-      </c>
-      <c r="F21" s="2">
-        <v>2228081.50</v>
-      </c>
-      <c r="G21" s="2">
+      <c r="D22" s="2">
+        <v>2613954.00</v>
+      </c>
+      <c r="E22" s="2">
+        <v>53437.50</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2560516.50</v>
+      </c>
+      <c r="G22" s="2">
         <v>0.00</v>
       </c>
-      <c r="H21" s="2">
-        <v>2228081.50</v>
-      </c>
-      <c r="I21" s="2">
+      <c r="H22" s="2">
+        <v>2560516.50</v>
+      </c>
+      <c r="I22" s="2">
         <v>0.00</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J22" s="2">
         <v>0.00</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K22" s="2">
         <v>900.00</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L22" s="2">
         <v>894.00</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M22" s="2">
         <v>0.00</v>
       </c>
-      <c r="N21" s="2">
-        <v>2227187.50</v>
-      </c>
-      <c r="O21" s="2">
+      <c r="N22" s="2">
+        <v>2559622.50</v>
+      </c>
+      <c r="O22" s="2">
         <v>0.00</v>
       </c>
-      <c r="P21" s="2">
-        <v>5488.50</v>
+      <c r="P22" s="2">
+        <v>6393.50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q20"/>
+  <autoFilter ref="A2:Q21"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
